--- a/slide_classification/TCGA_Results/Caption_based_aggregation/UNI2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/UNI2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J106" t="n">
         <v>1</v>
@@ -5081,7 +5081,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0.285714</v>
+        <v>0.333333</v>
       </c>
       <c r="J108" t="n">
         <v>1</v>
@@ -5124,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -5167,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J110" t="n">
         <v>1</v>
@@ -5210,7 +5210,7 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>0.142857</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -5425,7 +5425,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -5597,7 +5597,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>0.142857</v>
+        <v>0</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -5683,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0.285714</v>
+        <v>0.333333</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>0.285714</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -5984,7 +5984,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>0.142857</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
         <v>1</v>
@@ -6027,7 +6027,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>0.285714</v>
+        <v>0.333333</v>
       </c>
       <c r="J130" t="n">
         <v>1</v>
@@ -6070,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0.142857</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J132" t="n">
         <v>1</v>
@@ -6156,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>0.142857</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
         <v>1</v>
@@ -6199,7 +6199,7 @@
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -6328,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>0.142857</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -6672,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0.142857</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
         <v>1</v>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -6758,7 +6758,7 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>0.285714</v>
+        <v>0.333333</v>
       </c>
       <c r="J147" t="n">
         <v>1</v>
@@ -6844,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>0.428571</v>
+        <v>0.333333</v>
       </c>
       <c r="J151" t="n">
         <v>1</v>
@@ -6973,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>0.428571</v>
+        <v>0.333333</v>
       </c>
       <c r="J152" t="n">
         <v>1</v>
@@ -7016,7 +7016,7 @@
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>0.285714</v>
+        <v>0.333333</v>
       </c>
       <c r="J153" t="n">
         <v>1</v>
@@ -7056,10 +7056,10 @@
         <v>0.385856</v>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>0.285714</v>
+        <v>0.666667</v>
       </c>
       <c r="J154" t="n">
         <v>1</v>
@@ -7145,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>0.142857</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
         <v>1</v>
@@ -7188,7 +7188,7 @@
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>0.142857</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
         <v>1</v>
@@ -7231,7 +7231,7 @@
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>0.142857</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -7274,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>0.142857</v>
+        <v>0</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -7486,10 +7486,10 @@
         <v>0.286381</v>
       </c>
       <c r="H164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.285714</v>
+        <v>0.666667</v>
       </c>
       <c r="J164" t="n">
         <v>1</v>
@@ -7575,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J166" t="n">
         <v>1</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J168" t="n">
         <v>1</v>
@@ -7704,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>0.142857</v>
+        <v>0</v>
       </c>
       <c r="J169" t="n">
         <v>1</v>
@@ -7833,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>0.285714</v>
+        <v>0.333333</v>
       </c>
       <c r="J172" t="n">
         <v>1</v>
@@ -7919,7 +7919,7 @@
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>0.142857</v>
+        <v>0</v>
       </c>
       <c r="J174" t="n">
         <v>1</v>
@@ -8564,7 +8564,7 @@
         <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>0.142857</v>
+        <v>0</v>
       </c>
       <c r="J189" t="n">
         <v>1</v>
@@ -8607,7 +8607,7 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>0.285714</v>
+        <v>0.333333</v>
       </c>
       <c r="J190" t="n">
         <v>1</v>
@@ -8650,7 +8650,7 @@
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J191" t="n">
         <v>1</v>
@@ -8736,7 +8736,7 @@
         <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>0.285714</v>
+        <v>0.333333</v>
       </c>
       <c r="J193" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>0.285714</v>
+        <v>0</v>
       </c>
       <c r="J196" t="n">
         <v>1</v>
@@ -8908,7 +8908,7 @@
         <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>0.142857</v>
+        <v>0.333333</v>
       </c>
       <c r="J197" t="n">
         <v>1</v>
@@ -8951,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>0.142857</v>
+        <v>0</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -8994,7 +8994,7 @@
         <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>0.285714</v>
+        <v>0</v>
       </c>
       <c r="J199" t="n">
         <v>1</v>
@@ -14194,10 +14194,10 @@
         <v>0.544062</v>
       </c>
       <c r="H320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I320" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J320" t="n">
         <v>0</v>
@@ -14799,7 +14799,7 @@
         <v>0</v>
       </c>
       <c r="I334" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J334" t="n">
         <v>1</v>
@@ -15487,7 +15487,7 @@
         <v>0</v>
       </c>
       <c r="I350" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J350" t="n">
         <v>1</v>
@@ -16086,10 +16086,10 @@
         <v>0.981446</v>
       </c>
       <c r="H364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I364" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J364" t="n">
         <v>1</v>
@@ -16774,10 +16774,10 @@
         <v>0.696126</v>
       </c>
       <c r="H380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I380" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J380" t="n">
         <v>1</v>
@@ -16860,10 +16860,10 @@
         <v>0.526473</v>
       </c>
       <c r="H382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I382" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J382" t="n">
         <v>1</v>
@@ -17892,10 +17892,10 @@
         <v>0.174637</v>
       </c>
       <c r="H406" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I406" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J406" t="n">
         <v>0</v>
@@ -18236,10 +18236,10 @@
         <v>0.9401119999999999</v>
       </c>
       <c r="H414" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I414" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J414" t="n">
         <v>0</v>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation/UNI2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/UNI2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.244753</v>
+        <v>0.126674</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.163481</v>
+        <v>0.09450500000000001</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.147578</v>
+        <v>0.083912</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.994909</v>
+        <v>0.997965</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.22726</v>
+        <v>0.049941</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.576205</v>
+        <v>0.709636</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.12521</v>
+        <v>0.048525</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.15693</v>
+        <v>0.088866</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.156527</v>
+        <v>0.085215</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.12843</v>
+        <v>0.095107</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.307302</v>
+        <v>0.172672</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.36554</v>
+        <v>0.234781</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.335754</v>
+        <v>0.232058</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.186951</v>
+        <v>0.08956</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.877449</v>
+        <v>0.839387</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.149406</v>
+        <v>0.06460399999999999</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.30863</v>
+        <v>0.18174</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.946991</v>
+        <v>0.9606130000000001</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.896624</v>
+        <v>0.902782</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.20469</v>
+        <v>0.110071</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.201267</v>
+        <v>0.077178</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.246216</v>
+        <v>0.114984</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.14331</v>
+        <v>0.051115</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.146384</v>
+        <v>0.085234</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.767555</v>
+        <v>0.8636509999999999</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.315849</v>
+        <v>0.422015</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.184406</v>
+        <v>0.095248</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.269437</v>
+        <v>0.116838</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.174741</v>
+        <v>0.08625099999999999</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.248507</v>
+        <v>0.168371</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.231423</v>
+        <v>0.140552</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.128207</v>
+        <v>0.067264</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.230391</v>
+        <v>0.101077</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.230056</v>
+        <v>0.113776</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.310494</v>
+        <v>0.194547</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.128541</v>
+        <v>0.06739000000000001</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.294882</v>
+        <v>0.361811</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.221052</v>
+        <v>0.10646</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.30891</v>
+        <v>0.271035</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.342543</v>
+        <v>0.299333</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.198264</v>
+        <v>0.109463</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.414735</v>
+        <v>0.237166</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.195399</v>
+        <v>0.173805</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.193017</v>
+        <v>0.134652</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6835,10 +6835,10 @@
         <v>0.000109</v>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.58047</v>
+        <v>0.385072</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.164375</v>
+        <v>0.07953300000000001</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.889114</v>
+        <v>0.912824</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.998956</v>
+        <v>0.999908</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.256796</v>
+        <v>0.123931</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.385856</v>
+        <v>0.226912</v>
       </c>
       <c r="H154" t="n">
         <v>1</v>
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.278317</v>
+        <v>0.204764</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.200422</v>
+        <v>0.131134</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.267678</v>
+        <v>0.238837</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.184073</v>
+        <v>0.128578</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.182937</v>
+        <v>0.09193800000000001</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.165825</v>
+        <v>0.105342</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.11369</v>
+        <v>0.0536</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.192888</v>
+        <v>0.143355</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0.400048</v>
+        <v>0.376393</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.286381</v>
+        <v>0.148148</v>
       </c>
       <c r="H164" t="n">
         <v>1</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.168348</v>
+        <v>0.06900100000000001</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.393888</v>
+        <v>0.416684</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.170485</v>
+        <v>0.076932</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0.450941</v>
+        <v>0.460716</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.152841</v>
+        <v>0.073049</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.155409</v>
+        <v>0.08407299999999999</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.210866</v>
+        <v>0.127674</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.413244</v>
+        <v>0.321094</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.123336</v>
+        <v>0.050588</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.135895</v>
+        <v>0.050008</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.178436</v>
+        <v>0.09551800000000001</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.231334</v>
+        <v>0.166947</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.171761</v>
+        <v>0.062859</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.171328</v>
+        <v>0.104871</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.172602</v>
+        <v>0.088736</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.149632</v>
+        <v>0.08576300000000001</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0.407343</v>
+        <v>0.262375</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.378281</v>
+        <v>0.409944</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.130737</v>
+        <v>0.102127</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.202201</v>
+        <v>0.151065</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.214662</v>
+        <v>0.163827</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.174987</v>
+        <v>0.154962</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.240392</v>
+        <v>0.118115</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.233323</v>
+        <v>0.219249</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.207301</v>
+        <v>0.112386</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>0.5708569999999999</v>
+        <v>0.640873</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8644,7 +8644,7 @@
         <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>0.462552</v>
+        <v>0.408636</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0.23991</v>
+        <v>0.169993</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
         <v>1</v>
       </c>
       <c r="G193" t="n">
-        <v>0.887451</v>
+        <v>0.913252</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.202118</v>
+        <v>0.169543</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.212065</v>
+        <v>0.150406</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>1</v>
       </c>
       <c r="G196" t="n">
-        <v>0.637141</v>
+        <v>0.547746</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.95878</v>
+        <v>0.979683</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.72621</v>
+        <v>0.788913</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>0.637139</v>
+        <v>0.61842</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.273609</v>
+        <v>0.197272</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.15963</v>
+        <v>0.104894</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>0.222265</v>
+        <v>0.076449</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -9160,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.523596</v>
+        <v>0.623653</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
         <v>1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.6057169999999999</v>
+        <v>0.627628</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0.228938</v>
+        <v>0.148315</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>0.842179</v>
+        <v>0.943963</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>0.744787</v>
+        <v>0.673963</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0.1806</v>
+        <v>0.120346</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -9418,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>0.261067</v>
+        <v>0.146673</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>0.965992</v>
+        <v>0.998406</v>
       </c>
       <c r="H210" t="n">
         <v>1</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0.140623</v>
+        <v>0.038351</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>0.192556</v>
+        <v>0.061059</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9590,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>0.235276</v>
+        <v>0.09726899999999999</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>0.197242</v>
+        <v>0.065756</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>0.253844</v>
+        <v>0.09993299999999999</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -9719,7 +9719,7 @@
         <v>0</v>
       </c>
       <c r="G216" t="n">
-        <v>0.418946</v>
+        <v>0.29856</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0.151252</v>
+        <v>0.05259</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9805,7 +9805,7 @@
         <v>1</v>
       </c>
       <c r="G218" t="n">
-        <v>0.518626</v>
+        <v>0.644079</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9848,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0.290904</v>
+        <v>0.150789</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0.209902</v>
+        <v>0.067935</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>0.311107</v>
+        <v>0.159046</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -9977,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="G222" t="n">
-        <v>0.647804</v>
+        <v>0.771243</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>0.236132</v>
+        <v>0.096049</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -10063,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0.194662</v>
+        <v>0.061814</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>0.352333</v>
+        <v>0.21085</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>0.174743</v>
+        <v>0.070103</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="G227" t="n">
-        <v>0.295385</v>
+        <v>0.27419</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0.236802</v>
+        <v>0.09483900000000001</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0.192651</v>
+        <v>0.074643</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>0.18778</v>
+        <v>0.077307</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -10364,7 +10364,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.7884370000000001</v>
+        <v>0.914873</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0.457763</v>
+        <v>0.341714</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
         <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>0.821462</v>
+        <v>0.939094</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -10493,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>0.397239</v>
+        <v>0.391986</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="G235" t="n">
-        <v>0.93986</v>
+        <v>0.99086</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0.241973</v>
+        <v>0.161767</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -10622,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>0.139029</v>
+        <v>0.045819</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -10665,7 +10665,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0.197753</v>
+        <v>0.06514499999999999</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0.176927</v>
+        <v>0.042882</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>0.204752</v>
+        <v>0.08065799999999999</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>0.21012</v>
+        <v>0.115192</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0.125045</v>
+        <v>0.021614</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -10880,7 +10880,7 @@
         <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>0.271224</v>
+        <v>0.135097</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -10923,7 +10923,7 @@
         <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>0.284375</v>
+        <v>0.161891</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
         <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>0.620134</v>
+        <v>0.558651</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -11009,7 +11009,7 @@
         <v>1</v>
       </c>
       <c r="G246" t="n">
-        <v>0.877145</v>
+        <v>0.96958</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -11052,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="G247" t="n">
-        <v>0.9411310000000001</v>
+        <v>0.992646</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
         <v>1</v>
       </c>
       <c r="G248" t="n">
-        <v>0.5816210000000001</v>
+        <v>0.603826</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>0.970127</v>
+        <v>0.998377</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -11181,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>0.29309</v>
+        <v>0.174895</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>0.372616</v>
+        <v>0.290986</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -11267,7 +11267,7 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0.655897</v>
+        <v>0.840292</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>0.149887</v>
+        <v>0.065939</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>0.305398</v>
+        <v>0.172137</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>0.417943</v>
+        <v>0.407276</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>1</v>
       </c>
       <c r="G256" t="n">
-        <v>0.892449</v>
+        <v>0.956879</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -11482,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="G257" t="n">
-        <v>0.885034</v>
+        <v>0.971679</v>
       </c>
       <c r="H257" t="n">
         <v>1</v>
@@ -11525,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="G258" t="n">
-        <v>0.908948</v>
+        <v>0.869382</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>0.610464</v>
+        <v>0.68792</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>0.106718</v>
+        <v>0.062961</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0.583713</v>
+        <v>0.542961</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -11694,10 +11694,10 @@
         <v>0.225498</v>
       </c>
       <c r="F262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G262" t="n">
-        <v>0.514849</v>
+        <v>0.440249</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>0.184441</v>
+        <v>0.087423</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -11783,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>0.895488</v>
+        <v>0.947269</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -11826,7 +11826,7 @@
         <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>0.148168</v>
+        <v>0.089672</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>0.11125</v>
+        <v>0.039997</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>0.817001</v>
+        <v>0.913218</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>1</v>
       </c>
       <c r="G268" t="n">
-        <v>0.9106109999999999</v>
+        <v>0.984371</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>0.187546</v>
+        <v>0.100212</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -12041,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0.236276</v>
+        <v>0.109822</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>0.115503</v>
+        <v>0.059135</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -12127,7 +12127,7 @@
         <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>0.395184</v>
+        <v>0.359453</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -12170,7 +12170,7 @@
         <v>1</v>
       </c>
       <c r="G273" t="n">
-        <v>0.608927</v>
+        <v>0.523883</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -12213,7 +12213,7 @@
         <v>1</v>
       </c>
       <c r="G274" t="n">
-        <v>0.527595</v>
+        <v>0.551809</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>1</v>
       </c>
       <c r="G275" t="n">
-        <v>0.508844</v>
+        <v>0.555539</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -12299,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="G276" t="n">
-        <v>0.501946</v>
+        <v>0.618004</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -12342,7 +12342,7 @@
         <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>0.442381</v>
+        <v>0.403502</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -12385,7 +12385,7 @@
         <v>0</v>
       </c>
       <c r="G278" t="n">
-        <v>0.24786</v>
+        <v>0.183481</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -12428,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>0.252105</v>
+        <v>0.157821</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -12471,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>0.167138</v>
+        <v>0.076464</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -12514,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0.300932</v>
+        <v>0.187543</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>0.191695</v>
+        <v>0.098719</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>0.149065</v>
+        <v>0.081465</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>0.129138</v>
+        <v>0.081638</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -12686,7 +12686,7 @@
         <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>0.235284</v>
+        <v>0.117737</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="G286" t="n">
-        <v>0.401087</v>
+        <v>0.186154</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -12769,10 +12769,10 @@
         <v>0.07320400000000001</v>
       </c>
       <c r="F287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G287" t="n">
-        <v>0.671754</v>
+        <v>0.472096</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -12815,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>0.302518</v>
+        <v>0.183957</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>0.196559</v>
+        <v>0.128824</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="G290" t="n">
-        <v>0.228844</v>
+        <v>0.129259</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>0.229192</v>
+        <v>0.104007</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>0</v>
       </c>
       <c r="G292" t="n">
-        <v>0.231048</v>
+        <v>0.189926</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -13030,7 +13030,7 @@
         <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>0.26405</v>
+        <v>0.229368</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -13073,7 +13073,7 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>0.120467</v>
+        <v>0.040207</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>0.117003</v>
+        <v>0.056001</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -13159,7 +13159,7 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0.988078</v>
+        <v>0.998908</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -13202,7 +13202,7 @@
         <v>0</v>
       </c>
       <c r="G297" t="n">
-        <v>0.478417</v>
+        <v>0.310616</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>0.362264</v>
+        <v>0.233268</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0.679493</v>
+        <v>0.537519</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -13328,10 +13328,10 @@
         <v>0.050366</v>
       </c>
       <c r="F300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G300" t="n">
-        <v>0.523713</v>
+        <v>0.349986</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0.21706</v>
+        <v>0.101546</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="G302" t="n">
-        <v>0.431463</v>
+        <v>0.270784</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -13460,7 +13460,7 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0.897139</v>
+        <v>0.978994</v>
       </c>
       <c r="H303" t="n">
         <v>1</v>
@@ -13503,7 +13503,7 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0.980521</v>
+        <v>0.998981</v>
       </c>
       <c r="H304" t="n">
         <v>1</v>
@@ -13546,7 +13546,7 @@
         <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>0.175862</v>
+        <v>0.08372499999999999</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>0.296344</v>
+        <v>0.217287</v>
       </c>
       <c r="H306" t="n">
         <v>1</v>
@@ -13632,7 +13632,7 @@
         <v>0</v>
       </c>
       <c r="G307" t="n">
-        <v>0.252388</v>
+        <v>0.215027</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13675,7 +13675,7 @@
         <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>0.234705</v>
+        <v>0.150474</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -13718,7 +13718,7 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0.868125</v>
+        <v>0.932775</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -13761,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0.240986</v>
+        <v>0.065688</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
         <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>0.326977</v>
+        <v>0.128356</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>0.256034</v>
+        <v>0.107672</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -13890,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>0.236981</v>
+        <v>0.133094</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.162671</v>
+        <v>0.060224</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.153952</v>
+        <v>0.10647</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.217115</v>
+        <v>0.259543</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.152982</v>
+        <v>0.114939</v>
       </c>
       <c r="H317" t="n">
         <v>1</v>
@@ -14105,7 +14105,7 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0.794266</v>
+        <v>0.816296</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14148,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="G319" t="n">
-        <v>0.390526</v>
+        <v>0.349518</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14188,10 +14188,10 @@
         <v>4.1e-05</v>
       </c>
       <c r="F320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G320" t="n">
-        <v>0.544062</v>
+        <v>0.453403</v>
       </c>
       <c r="H320" t="n">
         <v>1</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.133986</v>
+        <v>0.131678</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14277,7 +14277,7 @@
         <v>0</v>
       </c>
       <c r="G322" t="n">
-        <v>0.166266</v>
+        <v>0.17236</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.12097</v>
+        <v>0.089113</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.177793</v>
+        <v>0.160238</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.103902</v>
+        <v>0.060314</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0.292858</v>
+        <v>0.224482</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>0.20784</v>
+        <v>0.180385</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14535,7 +14535,7 @@
         <v>1</v>
       </c>
       <c r="G328" t="n">
-        <v>0.805041</v>
+        <v>0.847243</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0.142107</v>
+        <v>0.102249</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.133423</v>
+        <v>0.125234</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.99621</v>
+        <v>0.996442</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.114603</v>
+        <v>0.07936699999999999</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0.994982</v>
+        <v>0.998853</v>
       </c>
       <c r="H333" t="n">
         <v>1</v>
@@ -14793,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>0.433274</v>
+        <v>0.367294</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0.209299</v>
+        <v>0.142328</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14879,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>0.10408</v>
+        <v>0.081913</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14922,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>0.07964499999999999</v>
+        <v>0.033257</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0.117724</v>
+        <v>0.073892</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.08931500000000001</v>
+        <v>0.065346</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.247641</v>
+        <v>0.24389</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.163594</v>
+        <v>0.09631099999999999</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.098949</v>
+        <v>0.077205</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.09689399999999999</v>
+        <v>0.061115</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.070123</v>
+        <v>0.041562</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15266,7 +15266,7 @@
         <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>0.20969</v>
+        <v>0.138256</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0.127307</v>
+        <v>0.131571</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15352,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0.17178</v>
+        <v>0.121157</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0.07016699999999999</v>
       </c>
       <c r="F348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>0.445397</v>
+        <v>0.6655219999999999</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -15438,7 +15438,7 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>0.799556</v>
+        <v>0.855262</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>1</v>
       </c>
       <c r="G350" t="n">
-        <v>0.7761400000000001</v>
+        <v>0.794521</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.405604</v>
+        <v>0.397866</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -15567,7 +15567,7 @@
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.225911</v>
+        <v>0.145771</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.140748</v>
+        <v>0.06609</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.09678100000000001</v>
+        <v>0.107006</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.068498</v>
+        <v>0.035084</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0.078347</v>
+        <v>0.04459</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.130001</v>
+        <v>0.064702</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>0</v>
       </c>
       <c r="G358" t="n">
-        <v>0.158654</v>
+        <v>0.17609</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -15868,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0.078032</v>
+        <v>0.020851</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15908,10 +15908,10 @@
         <v>0.010378</v>
       </c>
       <c r="F360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>0.521498</v>
+        <v>0.38517</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>0.72539</v>
+        <v>0.798372</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15997,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0.986822</v>
+        <v>0.996151</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.090646</v>
+        <v>0.044538</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16083,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0.981446</v>
+        <v>0.992992</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.164213</v>
+        <v>0.096273</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>0.255979</v>
+        <v>0.139892</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>0.602345</v>
+        <v>0.790546</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.408823</v>
+        <v>0.362958</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>0.435189</v>
+        <v>0.366357</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.15426</v>
+        <v>0.10879</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16384,7 +16384,7 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0.923837</v>
+        <v>0.974413</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>0.158287</v>
+        <v>0.156204</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.136414</v>
+        <v>0.074545</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0.208025</v>
+        <v>0.270195</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.268445</v>
+        <v>0.204753</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>0.134559</v>
+        <v>0.071593</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.168341</v>
+        <v>0.14561</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0.376261</v>
+        <v>0.358902</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>0.344922</v>
+        <v>0.393363</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16771,7 +16771,7 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0.696126</v>
+        <v>0.72215</v>
       </c>
       <c r="H380" t="n">
         <v>1</v>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.367212</v>
+        <v>0.299477</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16857,7 +16857,7 @@
         <v>1</v>
       </c>
       <c r="G382" t="n">
-        <v>0.526473</v>
+        <v>0.759551</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.075471</v>
+        <v>0.03272</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.124736</v>
+        <v>0.07405</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.056017</v>
+        <v>0.022383</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.06542100000000001</v>
+        <v>0.036239</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17072,7 +17072,7 @@
         <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>0.239805</v>
+        <v>0.249982</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.216523</v>
+        <v>0.144137</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.106787</v>
+        <v>0.040428</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.186021</v>
+        <v>0.211412</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="G391" t="n">
-        <v>0.383563</v>
+        <v>0.308843</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>0.531618</v>
+        <v>0.591025</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0.71038</v>
+        <v>0.908872</v>
       </c>
       <c r="H393" t="n">
         <v>1</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.156149</v>
+        <v>0.1152</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
         <v>1</v>
       </c>
       <c r="G395" t="n">
-        <v>0.719683</v>
+        <v>0.725824</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.282996</v>
+        <v>0.282926</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17499,10 +17499,10 @@
         <v>0.015878</v>
       </c>
       <c r="F397" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G397" t="n">
-        <v>0.5126810000000001</v>
+        <v>0.455457</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.417047</v>
+        <v>0.386402</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.168199</v>
+        <v>0.095512</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.242139</v>
+        <v>0.189431</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
         <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>0.340061</v>
+        <v>0.291613</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.132564</v>
+        <v>0.067591</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -17760,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>0.97512</v>
+        <v>0.972108</v>
       </c>
       <c r="H403" t="n">
         <v>1</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.142593</v>
+        <v>0.06617000000000001</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.107771</v>
+        <v>0.059583</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.174637</v>
+        <v>0.152785</v>
       </c>
       <c r="H406" t="n">
         <v>1</v>
@@ -17932,7 +17932,7 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0.63166</v>
+        <v>0.620108</v>
       </c>
       <c r="H407" t="n">
         <v>1</v>
@@ -17975,7 +17975,7 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0.996214</v>
+        <v>0.999099</v>
       </c>
       <c r="H408" t="n">
         <v>1</v>
@@ -18015,10 +18015,10 @@
         <v>1.6e-05</v>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>0.560658</v>
+        <v>0.376826</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.084608</v>
+        <v>0.028732</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0.591238</v>
+        <v>0.5773</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18147,7 +18147,7 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0.5621660000000001</v>
+        <v>0.500453</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>0.220704</v>
+        <v>0.080984</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0.9401119999999999</v>
+        <v>0.930027</v>
       </c>
       <c r="H414" t="n">
         <v>1</v>
